--- a/CHARMS CADENAS DE SEGURIDAD.xlsx
+++ b/CHARMS CADENAS DE SEGURIDAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87E354DF-D90E-44D1-9087-8CA2EC3E5FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD973B1D-5E4C-4F11-8E71-EE155AD23AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96D19110-95BC-4F1F-B696-F8CC57CE91CD}"/>
   </bookViews>
@@ -3392,9 +3392,7 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I11" s="10">
-        <v>2</v>
-      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
@@ -3423,9 +3421,7 @@
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>1</v>
-      </c>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
@@ -3504,9 +3500,7 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
     </row>

--- a/CHARMS CADENAS DE SEGURIDAD.xlsx
+++ b/CHARMS CADENAS DE SEGURIDAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD973B1D-5E4C-4F11-8E71-EE155AD23AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ED40DA-727C-4F67-A0C2-CD2275626D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96D19110-95BC-4F1F-B696-F8CC57CE91CD}"/>
   </bookViews>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="8">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="D5" s="9">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>35.64</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>71.28</v>
       </c>
       <c r="F5" s="9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
